--- a/outputs/daily/hr_rankings_2026-10-26.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-26.xlsx
@@ -840,12 +840,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.4</v>
+        <v>57.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>54.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -907,39 +907,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1084,7 +1080,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1200,12 +1196,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1224,7 +1220,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>56.3</v>
+        <v>57.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1238,7 +1234,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1251,7 +1247,7 @@
         <v>54.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1265,39 +1261,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1442,7 +1434,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1518,7 +1510,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1542,7 +1534,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.9</v>
+        <v>53.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1556,7 +1548,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1569,7 +1561,7 @@
         <v>54.1</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1583,39 +1575,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1760,7 +1748,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1811,12 +1799,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1836,7 +1824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1860,7 +1848,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1874,11 +1862,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>43.3</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
@@ -1887,13 +1875,13 @@
         <v>54.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1901,39 +1889,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1953,7 +1937,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1963,17 +1947,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1983,67 +1967,67 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2078,7 +2062,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2129,24 +2113,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -2154,31 +2138,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2192,26 +2176,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.6</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R6" t="n">
         <v>54.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>65.2</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2219,39 +2203,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2271,27 +2251,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2301,102 +2281,102 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2447,24 +2427,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -2472,31 +2452,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.4</v>
+        <v>50.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2510,26 +2490,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
         <v>54.1</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2537,39 +2517,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2589,27 +2565,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2619,102 +2595,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2765,24 +2741,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -2790,31 +2766,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2828,26 +2804,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R8" t="n">
         <v>54.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2855,39 +2831,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2907,27 +2879,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2937,102 +2909,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3108,12 +3080,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3132,7 +3104,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>50.9</v>
+        <v>50.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,7 +3118,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -3159,7 +3131,7 @@
         <v>54.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -3173,39 +3145,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3350,7 +3318,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3426,7 +3394,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3450,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,7 +3432,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3477,7 +3445,7 @@
         <v>54.1</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -3491,39 +3459,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3668,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3719,24 +3683,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -3744,31 +3708,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.3</v>
+        <v>48.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,26 +3746,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>43.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R11" t="n">
         <v>54.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3809,39 +3773,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3861,12 +3821,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -3876,12 +3836,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3891,102 +3851,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4062,12 +4022,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4086,7 +4046,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43.5</v>
+        <v>42.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,7 +4060,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -4113,7 +4073,7 @@
         <v>54.1</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -4127,39 +4087,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4304,7 +4260,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4355,12 +4311,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4380,12 +4336,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4404,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>39.2</v>
+        <v>40.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,11 +4374,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q13" t="n">
         <v>38.7</v>
@@ -4431,13 +4387,13 @@
         <v>54.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4445,39 +4401,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4502,7 +4454,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -4512,7 +4464,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -4527,67 +4479,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4622,7 +4574,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4698,12 +4650,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4722,7 +4674,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>38.5</v>
+        <v>37.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,7 +4688,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4749,7 +4701,7 @@
         <v>54.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -4763,39 +4715,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4940,7 +4888,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4991,24 +4939,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -5016,31 +4964,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35.5</v>
+        <v>37.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,26 +5002,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.6</v>
+        <v>38.7</v>
       </c>
       <c r="R15" t="n">
         <v>54.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>5.1</v>
+        <v>15.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5081,42 +5029,38 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -5133,12 +5077,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5148,12 +5092,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5163,102 +5107,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5334,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5358,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.6</v>
+        <v>35.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5372,7 +5316,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -5385,7 +5329,7 @@
         <v>54.1</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
@@ -5399,39 +5343,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5576,7 +5516,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5652,7 +5592,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5676,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.4</v>
+        <v>35</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,7 +5630,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5703,7 +5643,7 @@
         <v>54.1</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -5717,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5894,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5945,12 +5881,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5970,12 +5906,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5994,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6008,26 +5944,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.7</v>
+        <v>37.5</v>
       </c>
       <c r="R18" t="n">
         <v>54.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6035,39 +5971,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6092,7 +6024,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6102,12 +6034,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6117,67 +6049,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6212,7 +6144,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6263,24 +6195,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -6288,64 +6220,64 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L19" t="n">
+        <v>34</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Platoon Edge</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q19" t="n">
         <v>33.4</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Projected Lineup, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>37.5</v>
       </c>
       <c r="R19" t="n">
         <v>54.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6353,39 +6285,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6405,12 +6333,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -6420,12 +6348,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6435,102 +6363,102 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7012,12 +6940,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7036,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.4</v>
+        <v>57.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7050,7 +6978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7063,7 +6991,7 @@
         <v>54.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -7079,39 +7007,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7256,7 +7180,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7372,12 +7296,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7396,7 +7320,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>56.3</v>
+        <v>57.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7410,7 +7334,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7423,7 +7347,7 @@
         <v>54.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -7437,39 +7361,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7614,7 +7534,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7690,7 +7610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7714,7 +7634,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.9</v>
+        <v>53.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7728,7 +7648,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7741,7 +7661,7 @@
         <v>54.1</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -7755,39 +7675,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7932,7 +7848,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7983,12 +7899,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8008,7 +7924,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8032,7 +7948,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8046,11 +7962,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>43.3</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
@@ -8059,13 +7975,13 @@
         <v>54.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -8073,39 +7989,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8125,7 +8037,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -8135,17 +8047,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -8155,67 +8067,67 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -8250,7 +8162,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8301,24 +8213,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -8326,31 +8238,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8364,26 +8276,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.6</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R6" t="n">
         <v>54.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>65.2</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8391,39 +8303,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8443,27 +8351,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8473,102 +8381,102 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8619,24 +8527,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -8644,31 +8552,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.4</v>
+        <v>50.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8682,26 +8590,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
         <v>54.1</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8709,39 +8617,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8761,27 +8665,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8791,102 +8695,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8937,24 +8841,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -8962,31 +8866,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9000,26 +8904,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R8" t="n">
         <v>54.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -9027,39 +8931,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9079,27 +8979,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -9109,102 +9009,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9280,12 +9180,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9304,7 +9204,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>50.9</v>
+        <v>50.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9318,7 +9218,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -9331,7 +9231,7 @@
         <v>54.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -9345,39 +9245,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9522,7 +9418,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9598,7 +9494,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9622,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,7 +9532,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9649,7 +9545,7 @@
         <v>54.1</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -9663,39 +9559,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9840,7 +9732,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9891,24 +9783,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -9916,31 +9808,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.3</v>
+        <v>48.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,26 +9846,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>43.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R11" t="n">
         <v>54.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9981,39 +9873,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10033,12 +9921,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -10048,12 +9936,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -10063,102 +9951,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10234,12 +10122,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -10258,7 +10146,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43.5</v>
+        <v>42.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,7 +10160,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -10285,7 +10173,7 @@
         <v>54.1</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -10299,39 +10187,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10476,7 +10360,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10527,12 +10411,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10552,12 +10436,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10576,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>39.2</v>
+        <v>40.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10590,11 +10474,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q13" t="n">
         <v>38.7</v>
@@ -10603,13 +10487,13 @@
         <v>54.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10617,39 +10501,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10674,7 +10554,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -10684,7 +10564,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -10699,67 +10579,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -10794,7 +10674,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10870,12 +10750,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10894,7 +10774,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>38.5</v>
+        <v>37.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,7 +10788,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10921,7 +10801,7 @@
         <v>54.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -10935,39 +10815,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11112,7 +10988,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11163,24 +11039,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -11188,31 +11064,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35.5</v>
+        <v>37.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,26 +11102,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.6</v>
+        <v>38.7</v>
       </c>
       <c r="R15" t="n">
         <v>54.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>5.1</v>
+        <v>15.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11253,42 +11129,38 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -11305,12 +11177,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11320,12 +11192,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11335,102 +11207,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11506,7 +11378,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11530,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.6</v>
+        <v>35.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11544,7 +11416,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -11557,7 +11429,7 @@
         <v>54.1</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
@@ -11571,39 +11443,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11748,7 +11616,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11824,7 +11692,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11848,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.4</v>
+        <v>35</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,7 +11730,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -11875,7 +11743,7 @@
         <v>54.1</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -11889,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12066,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12117,12 +11981,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12142,12 +12006,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12166,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12180,26 +12044,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.7</v>
+        <v>37.5</v>
       </c>
       <c r="R18" t="n">
         <v>54.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12207,39 +12071,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12264,7 +12124,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12274,12 +12134,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12289,67 +12149,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12384,7 +12244,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12435,24 +12295,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -12460,64 +12320,64 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L19" t="n">
+        <v>34</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Platoon Edge</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q19" t="n">
         <v>33.4</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Projected Lineup, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>37.5</v>
       </c>
       <c r="R19" t="n">
         <v>54.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12525,39 +12385,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12577,12 +12433,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -12592,12 +12448,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12607,102 +12463,102 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>30 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-26.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-26.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
